--- a/attachments/DSJ_AE_Sustainable_Operations_and_Circular_Economy.xlsx
+++ b/attachments/DSJ_AE_Sustainable_Operations_and_Circular_Economy.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liangfeiqiu\Dropbox\UF\Review\DSJ EIC\DSJ EIC\DSJ board\Finalized\DSJ AEs and ERBs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A3F97A-F674-4868-A6E1-C5BF8E7ADAA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7404E72-6D65-4732-95BD-F08251576FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Z_233002E8_F7D1_42B5_BE95_3A5F3AABF9AC_.wvu.FilterData" localSheetId="0" hidden="1">'Form Responses 1'!$A$1:$L$26</definedName>
+    <definedName name="Z_233002E8_F7D1_42B5_BE95_3A5F3AABF9AC_.wvu.FilterData" localSheetId="0" hidden="1">'Form Responses 1'!$A$1:$L$29</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <customWorkbookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="244">
   <si>
     <t>First Name</t>
   </si>
@@ -727,6 +727,42 @@
   </si>
   <si>
     <t>College of Business</t>
+  </si>
+  <si>
+    <t>Jeff Zeyun</t>
+  </si>
+  <si>
+    <t>Chen</t>
+  </si>
+  <si>
+    <t>Texas Christian University</t>
+  </si>
+  <si>
+    <t>zeyun.chen@tcu.edu</t>
+  </si>
+  <si>
+    <t>Alper</t>
+  </si>
+  <si>
+    <t>Darendeli</t>
+  </si>
+  <si>
+    <t>adarendeli@ntu.edu.sg</t>
+  </si>
+  <si>
+    <t>Guoman</t>
+  </si>
+  <si>
+    <t>She</t>
+  </si>
+  <si>
+    <t>National University of Singapore</t>
+  </si>
+  <si>
+    <t>guoman.she@nus.edu.sg</t>
+  </si>
+  <si>
+    <t>Nanyang Technological University</t>
   </si>
 </sst>
 </file>
@@ -1066,7 +1102,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L1000"/>
+  <dimension ref="A1:L1003"/>
   <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.88671875" style="2" customWidth="1"/>
@@ -1554,376 +1590,342 @@
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
     </row>
-    <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+    </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
+      <c r="A16" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>243</v>
+      </c>
       <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" spans="1:12" ht="14.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+    </row>
+    <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="6"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+    </row>
+    <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+    </row>
+    <row r="20" spans="1:12" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B20" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C20" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D20" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E20" s="8" t="s">
         <v>106</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="14.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="14.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="14.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>131</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>17</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="8" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="H21" s="8" t="s">
-        <v>141</v>
-      </c>
       <c r="I21" s="8" t="s">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="8" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>17</v>
       </c>
       <c r="G22" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H22" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="H22" s="8" t="s">
-        <v>141</v>
-      </c>
       <c r="I22" s="8" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="8" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>17</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="8" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>17</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>29</v>
+        <v>141</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>165</v>
+        <v>32</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>167</v>
+        <v>31</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>32</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="8" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>17</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
+        <v>149</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="26" spans="1:12" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="8" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>17</v>
@@ -1932,106 +1934,108 @@
         <v>29</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
+        <v>32</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="27" spans="1:12" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="8" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>17</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>44</v>
+        <v>167</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>189</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="8" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>17</v>
       </c>
       <c r="G28" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H28" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="H28" s="8" t="s">
-        <v>141</v>
-      </c>
       <c r="I28" s="8" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="K28" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="L28" s="13"/>
+        <v>174</v>
+      </c>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
     </row>
     <row r="29" spans="1:12" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="8" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>17</v>
@@ -2040,110 +2044,215 @@
         <v>29</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K29" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="L29" s="8" t="s">
-        <v>203</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
     </row>
     <row r="30" spans="1:12" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="8" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>17</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>124</v>
+        <v>44</v>
       </c>
       <c r="L30" s="8" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="8" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>17</v>
       </c>
       <c r="G31" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H31" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="H31" s="8" t="s">
+      <c r="I31" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="K31" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="L31" s="13"/>
+    </row>
+    <row r="32" spans="1:12" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G32" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="I31" s="8" t="s">
+      <c r="H32" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K32" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="J31" s="8" t="s">
+      <c r="L32" s="8" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J34" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
-    </row>
-    <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+    </row>
+    <row r="35" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="36" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="37" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="38" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="39" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="40" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="41" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="42" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="43" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="44" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="45" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="46" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="47" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="48" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -3096,11 +3205,14 @@
     <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <customSheetViews>
     <customSheetView guid="{233002E8-F7D1-42B5-BE95-3A5F3AABF9AC}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:L25" xr:uid="{AA40AF06-6668-4BA7-87CA-B37A6D54056F}"/>
+      <autoFilter ref="A1:L25" xr:uid="{5160F3E8-904C-48AD-A5A3-88FBB08D0878}"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">
           <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="1955316490"/>
@@ -3109,11 +3221,11 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="1">
-    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="K31:L31"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C28" r:id="rId2" xr:uid="{93836D46-6578-4A49-81CA-746716C749E5}"/>
+    <hyperlink ref="C31" r:id="rId2" xr:uid="{93836D46-6578-4A49-81CA-746716C749E5}"/>
     <hyperlink ref="C13" r:id="rId3" xr:uid="{8C7AA49F-D682-4DE0-9BAD-D9FE05881DDB}"/>
     <hyperlink ref="C14" r:id="rId4" xr:uid="{CCD1DB78-E43B-488D-8564-1B58C68C9033}"/>
   </hyperlinks>
